--- a/data/model_criteria.xlsx
+++ b/data/model_criteria.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27928"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\baitlist\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B55137-1D40-47EA-9180-84C32F01523E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C33F5C-224B-43F0-BB69-E4F32B9FBA73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="model_criteria" sheetId="2" r:id="rId1"/>
@@ -36,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="70">
   <si>
     <t xml:space="preserve">Expected additional ICU length of stay </t>
   </si>
@@ -194,21 +189,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Cardiovascular</t>
-  </si>
-  <si>
-    <t>Pulmonary</t>
-  </si>
-  <si>
-    <t>Renal</t>
-  </si>
-  <si>
-    <t>Neurological</t>
-  </si>
-  <si>
-    <t>Gastro-intestinal</t>
-  </si>
-  <si>
     <t>ID_Alternative</t>
   </si>
   <si>
@@ -224,9 +204,6 @@
     <t>frailty</t>
   </si>
   <si>
-    <t>life</t>
-  </si>
-  <si>
     <t>life_expectancy</t>
   </si>
   <si>
@@ -249,6 +226,21 @@
   </si>
   <si>
     <t>family_values</t>
+  </si>
+  <si>
+    <t>Cardiovascular impairment</t>
+  </si>
+  <si>
+    <t>Pulmonary impairment</t>
+  </si>
+  <si>
+    <t>Renal impairment</t>
+  </si>
+  <si>
+    <t>Neurological impairment</t>
+  </si>
+  <si>
+    <t>Gastro-intestinal impairment</t>
   </si>
 </sst>
 </file>
@@ -645,7 +637,7 @@
         <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>37</v>
@@ -662,7 +654,7 @@
         <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
@@ -679,7 +671,7 @@
         <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
         <v>0</v>
@@ -696,7 +688,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -713,7 +705,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
         <v>3</v>
@@ -730,7 +722,7 @@
         <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
         <v>50</v>
@@ -747,7 +739,7 @@
         <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
         <v>50</v>
@@ -764,7 +756,7 @@
         <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
         <v>50</v>
@@ -781,7 +773,7 @@
         <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
         <v>50</v>
@@ -798,7 +790,7 @@
         <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
         <v>6</v>
@@ -815,7 +807,7 @@
         <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
         <v>6</v>
@@ -832,7 +824,7 @@
         <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
         <v>6</v>
@@ -849,7 +841,7 @@
         <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
@@ -866,7 +858,7 @@
         <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C14" t="s">
         <v>7</v>
@@ -883,7 +875,7 @@
         <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
         <v>7</v>
@@ -900,7 +892,7 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
@@ -917,7 +909,7 @@
         <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
@@ -934,10 +926,10 @@
         <v>44</v>
       </c>
       <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s">
         <v>65</v>
-      </c>
-      <c r="C18" t="s">
-        <v>52</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -951,10 +943,10 @@
         <v>44</v>
       </c>
       <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" t="s">
         <v>65</v>
-      </c>
-      <c r="C19" t="s">
-        <v>52</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -968,10 +960,10 @@
         <v>44</v>
       </c>
       <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
         <v>65</v>
-      </c>
-      <c r="C20" t="s">
-        <v>52</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -985,10 +977,10 @@
         <v>44</v>
       </c>
       <c r="B21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" t="s">
         <v>65</v>
-      </c>
-      <c r="C21" t="s">
-        <v>52</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -1002,10 +994,10 @@
         <v>45</v>
       </c>
       <c r="B22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" t="s">
         <v>66</v>
-      </c>
-      <c r="C22" t="s">
-        <v>53</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1019,10 +1011,10 @@
         <v>45</v>
       </c>
       <c r="B23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" t="s">
         <v>66</v>
-      </c>
-      <c r="C23" t="s">
-        <v>53</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1036,10 +1028,10 @@
         <v>45</v>
       </c>
       <c r="B24" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" t="s">
         <v>66</v>
-      </c>
-      <c r="C24" t="s">
-        <v>53</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -1053,10 +1045,10 @@
         <v>46</v>
       </c>
       <c r="B25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" t="s">
         <v>67</v>
-      </c>
-      <c r="C25" t="s">
-        <v>54</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1070,10 +1062,10 @@
         <v>46</v>
       </c>
       <c r="B26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" t="s">
         <v>67</v>
-      </c>
-      <c r="C26" t="s">
-        <v>54</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1087,10 +1079,10 @@
         <v>46</v>
       </c>
       <c r="B27" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" t="s">
         <v>67</v>
-      </c>
-      <c r="C27" t="s">
-        <v>54</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -1104,10 +1096,10 @@
         <v>47</v>
       </c>
       <c r="B28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" t="s">
         <v>68</v>
-      </c>
-      <c r="C28" t="s">
-        <v>55</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1121,10 +1113,10 @@
         <v>47</v>
       </c>
       <c r="B29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" t="s">
         <v>68</v>
-      </c>
-      <c r="C29" t="s">
-        <v>55</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1138,10 +1130,10 @@
         <v>47</v>
       </c>
       <c r="B30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" t="s">
         <v>68</v>
-      </c>
-      <c r="C30" t="s">
-        <v>55</v>
       </c>
       <c r="D30">
         <v>2</v>
@@ -1155,10 +1147,10 @@
         <v>48</v>
       </c>
       <c r="B31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
         <v>69</v>
-      </c>
-      <c r="C31" t="s">
-        <v>56</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1172,10 +1164,10 @@
         <v>48</v>
       </c>
       <c r="B32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" t="s">
         <v>69</v>
-      </c>
-      <c r="C32" t="s">
-        <v>56</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -1189,7 +1181,7 @@
         <v>49</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C33" t="s">
         <v>29</v>
@@ -1206,7 +1198,7 @@
         <v>49</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C34" t="s">
         <v>29</v>
